--- a/artfynd/A 49802-2025 artfynd.xlsx
+++ b/artfynd/A 49802-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126016913</v>
+        <v>126016918</v>
       </c>
       <c r="B2" t="n">
-        <v>97245</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>658433</v>
+        <v>657761</v>
       </c>
       <c r="R2" t="n">
-        <v>7213170</v>
+        <v>7213484</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126016918</v>
+        <v>126016916</v>
       </c>
       <c r="B3" t="n">
-        <v>78738</v>
+        <v>79085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -823,7 +823,7 @@
         <v>657761</v>
       </c>
       <c r="R3" t="n">
-        <v>7213484</v>
+        <v>7213485</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126016916</v>
+        <v>126016915</v>
       </c>
       <c r="B4" t="n">
-        <v>78739</v>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>657761</v>
+        <v>658367</v>
       </c>
       <c r="R4" t="n">
-        <v>7213485</v>
+        <v>7213256</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126016915</v>
+        <v>126016913</v>
       </c>
       <c r="B5" t="n">
-        <v>92527</v>
+        <v>97989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>658367</v>
+        <v>658433</v>
       </c>
       <c r="R5" t="n">
-        <v>7213256</v>
+        <v>7213170</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
